--- a/diseases/d020/2026-2029.xlsx
+++ b/diseases/d020/2026-2029.xlsx
@@ -49906,12 +49906,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -49936,12 +49936,12 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N278" t="n">
@@ -49984,42 +49984,42 @@
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -50051,12 +50051,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -50129,40 +50129,185 @@
       </c>
       <c r="AV279" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA279" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB279" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC279" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr"/>
+      <c r="AT280" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW279" t="inlineStr">
+      <c r="AW280" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX279" t="inlineStr">
+      <c r="AX280" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY279" t="inlineStr">
+      <c r="AY280" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ279" t="inlineStr">
+      <c r="AZ280" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA279" t="inlineStr">
+      <c r="BA280" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB279" t="inlineStr">
+      <c r="BB280" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC279" t="inlineStr">
+      <c r="BC280" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -50284,7 +50429,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -50294,7 +50439,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d020/2026-2029.xlsx
+++ b/diseases/d020/2026-2029.xlsx
@@ -47605,12 +47605,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -47644,13 +47644,16 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="O265" t="n">
-        <v>0</v>
+        <v>39</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>2</v>
       </c>
       <c r="R265" t="n">
-        <v>0</v>
+        <v>0.002760252751206111</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
@@ -47683,42 +47686,42 @@
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -47750,12 +47753,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -47780,7 +47783,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -47828,42 +47831,42 @@
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -47895,12 +47898,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -47939,9 +47942,6 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
-      <c r="P267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0</v>
       </c>
@@ -47950,77 +47950,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ267" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48047,7 +48038,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -48099,98 +48090,18 @@
       <c r="P268" t="n">
         <v>0</v>
       </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="W268" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X268" t="inlineStr">
-        <is>
-          <t>Japanese Encephalitis</t>
-        </is>
-      </c>
-      <c r="Y268" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R268" t="n">
+        <v>0</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD268" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE268" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF268" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG268" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI268" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ268" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK268" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM268" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN268" t="b">
-        <v>1</v>
       </c>
       <c r="AO268" t="inlineStr">
         <is>
@@ -48284,17 +48195,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -48319,7 +48230,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -48333,76 +48244,168 @@
       <c r="O269" t="n">
         <v>0</v>
       </c>
-      <c r="R269" t="n">
-        <v>0</v>
-      </c>
-      <c r="S269" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN269" t="b">
+        <v>1</v>
       </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48434,12 +48437,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -48478,9 +48481,6 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="P270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0</v>
       </c>
@@ -48489,77 +48489,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA270" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ270" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr"/>
       <c r="AT270" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48586,7 +48577,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -48638,98 +48629,18 @@
       <c r="P271" t="n">
         <v>0</v>
       </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="V271" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="W271" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X271" t="inlineStr">
-        <is>
-          <t>Japanese Encephalitis</t>
-        </is>
-      </c>
-      <c r="Y271" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R271" t="n">
+        <v>0</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB271" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD271" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE271" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF271" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG271" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH271" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI271" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ271" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK271" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM271" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN271" t="b">
-        <v>1</v>
       </c>
       <c r="AO271" t="inlineStr">
         <is>
@@ -48823,17 +48734,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -48858,7 +48769,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -48872,76 +48783,168 @@
       <c r="O272" t="n">
         <v>0</v>
       </c>
-      <c r="R272" t="n">
-        <v>0</v>
-      </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P272" t="n">
+        <v>0</v>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM272" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN272" t="b">
+        <v>1</v>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR272" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
       <c r="AT272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48973,12 +48976,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -49017,9 +49020,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="P273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -49028,77 +49028,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA273" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ273" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr"/>
       <c r="AT273" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49125,7 +49116,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -49177,98 +49168,18 @@
       <c r="P274" t="n">
         <v>0</v>
       </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="W274" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X274" t="inlineStr">
-        <is>
-          <t>Japanese Encephalitis</t>
-        </is>
-      </c>
-      <c r="Y274" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R274" t="n">
+        <v>0</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD274" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE274" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF274" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG274" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ274" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK274" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM274" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN274" t="b">
-        <v>1</v>
       </c>
       <c r="AO274" t="inlineStr">
         <is>
@@ -49362,17 +49273,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -49397,7 +49308,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -49411,76 +49322,168 @@
       <c r="O275" t="n">
         <v>0</v>
       </c>
-      <c r="R275" t="n">
-        <v>0</v>
-      </c>
-      <c r="S275" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P275" t="n">
+        <v>0</v>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ275" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM275" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN275" t="b">
+        <v>1</v>
       </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR275" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS275" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
       <c r="AT275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -49512,12 +49515,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -49556,9 +49559,6 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="P276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0</v>
       </c>
@@ -49567,77 +49567,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA276" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO276" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ276" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS276" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR276" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr"/>
       <c r="AT276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49664,7 +49655,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -49716,98 +49707,18 @@
       <c r="P277" t="n">
         <v>0</v>
       </c>
-      <c r="U277" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="W277" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X277" t="inlineStr">
-        <is>
-          <t>Japanese Encephalitis</t>
-        </is>
-      </c>
-      <c r="Y277" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R277" t="n">
+        <v>0</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB277" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD277" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE277" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF277" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG277" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI277" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ277" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK277" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM277" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN277" t="b">
-        <v>1</v>
       </c>
       <c r="AO277" t="inlineStr">
         <is>
@@ -49901,17 +49812,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -49936,7 +49847,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -49950,76 +49861,168 @@
       <c r="O278" t="n">
         <v>0</v>
       </c>
-      <c r="R278" t="n">
-        <v>0</v>
-      </c>
-      <c r="S278" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD278" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF278" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG278" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ278" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK278" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM278" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN278" t="b">
+        <v>1</v>
       </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR278" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
       <c r="AT278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -50051,12 +50054,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -50081,12 +50084,12 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N279" t="n">
@@ -50129,42 +50132,42 @@
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -50196,118 +50199,657 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N280" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
+      <c r="P280" t="n">
+        <v>0</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO280" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP280" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="AT280" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU280" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV280" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA280" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB280" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC280" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>0</v>
+      </c>
+      <c r="O281" t="n">
+        <v>0</v>
+      </c>
+      <c r="P281" t="n">
+        <v>0</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM281" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN281" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="AT281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV281" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB281" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC281" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr"/>
+      <c r="AT282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
+      <c r="G283" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>D020</t>
-        </is>
-      </c>
-      <c r="I280" t="inlineStr">
-        <is>
-          <t>Japanese Encephalitis</t>
-        </is>
-      </c>
-      <c r="J280" t="inlineStr">
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
         <is>
           <t>流行性乙型脑炎</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
+      <c r="K283" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
+      <c r="L283" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M280" t="inlineStr">
+      <c r="M283" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N280" t="n">
-        <v>0</v>
-      </c>
-      <c r="O280" t="n">
-        <v>0</v>
-      </c>
-      <c r="R280" t="n">
-        <v>0</v>
-      </c>
-      <c r="S280" t="inlineStr">
+      <c r="N283" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0</v>
+      </c>
+      <c r="R283" t="n">
+        <v>0</v>
+      </c>
+      <c r="S283" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO280" t="inlineStr">
+      <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP280" t="inlineStr">
+      <c r="AP283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR280" t="inlineStr">
+      <c r="AR283" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS280" t="inlineStr"/>
-      <c r="AT280" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU280" t="inlineStr">
+      <c r="AS283" t="inlineStr"/>
+      <c r="AT283" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU283" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV280" t="inlineStr">
+      <c r="AV283" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW280" t="inlineStr">
+      <c r="AW283" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX280" t="inlineStr">
+      <c r="AX283" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY280" t="inlineStr">
+      <c r="AY283" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ280" t="inlineStr">
+      <c r="AZ283" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA280" t="inlineStr">
+      <c r="BA283" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB280" t="inlineStr">
+      <c r="BB283" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC280" t="inlineStr">
+      <c r="BC283" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -50429,7 +50971,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -50439,7 +50981,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11">
@@ -50459,7 +51001,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -50491,7 +51033,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -50501,7 +51043,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d020/2026-2029.xlsx
+++ b/diseases/d020/2026-2029.xlsx
@@ -47792,13 +47792,13 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -51033,7 +51033,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d020/2026-2029.xlsx
+++ b/diseases/d020/2026-2029.xlsx
@@ -50855,6 +50855,151 @@
         </is>
       </c>
     </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N284" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="R284" t="n">
+        <v>0</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR284" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr"/>
+      <c r="AT284" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU284" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV284" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA284" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB284" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC284" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -50888,7 +51033,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -50971,7 +51116,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10">
@@ -50981,7 +51126,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d020/2026-2029.xlsx
+++ b/diseases/d020/2026-2029.xlsx
@@ -47792,13 +47792,13 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -51178,7 +51178,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d020/2026-2029.xlsx
+++ b/diseases/d020/2026-2029.xlsx
@@ -47792,13 +47792,13 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -50997,6 +50997,400 @@
       <c r="BC284" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" t="n">
+        <v>0</v>
+      </c>
+      <c r="P285" t="n">
+        <v>0</v>
+      </c>
+      <c r="R285" t="n">
+        <v>0</v>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP285" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ285" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="AT285" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV285" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA285" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB285" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC285" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N286" t="n">
+        <v>0</v>
+      </c>
+      <c r="O286" t="n">
+        <v>0</v>
+      </c>
+      <c r="P286" t="n">
+        <v>0</v>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ286" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK286" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM286" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN286" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP286" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="AT286" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU286" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV286" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA286" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB286" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC286" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -51116,7 +51510,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10">
@@ -51126,7 +51520,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11">
@@ -51146,7 +51540,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -51178,7 +51572,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d020/2026-2029.xlsx
+++ b/diseases/d020/2026-2029.xlsx
@@ -47753,12 +47753,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -47792,13 +47792,13 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -47831,42 +47831,42 @@
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -47898,12 +47898,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -47928,7 +47928,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -47937,13 +47937,13 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R267" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -47976,42 +47976,42 @@
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -48043,12 +48043,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -48087,9 +48087,6 @@
       <c r="O268" t="n">
         <v>0</v>
       </c>
-      <c r="P268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>0</v>
       </c>
@@ -48098,77 +48095,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ268" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
       <c r="AT268" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48195,7 +48183,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -48247,98 +48235,18 @@
       <c r="P269" t="n">
         <v>0</v>
       </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="V269" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="W269" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X269" t="inlineStr">
-        <is>
-          <t>Japanese Encephalitis</t>
-        </is>
-      </c>
-      <c r="Y269" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R269" t="n">
+        <v>0</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD269" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE269" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF269" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG269" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH269" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI269" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ269" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK269" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM269" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN269" t="b">
-        <v>1</v>
       </c>
       <c r="AO269" t="inlineStr">
         <is>
@@ -48432,17 +48340,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -48467,7 +48375,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -48481,76 +48389,168 @@
       <c r="O270" t="n">
         <v>0</v>
       </c>
-      <c r="R270" t="n">
-        <v>0</v>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P270" t="n">
+        <v>0</v>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN270" t="b">
+        <v>1</v>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
       <c r="AT270" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48582,12 +48582,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -48626,9 +48626,6 @@
       <c r="O271" t="n">
         <v>0</v>
       </c>
-      <c r="P271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0</v>
       </c>
@@ -48637,77 +48634,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ271" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr"/>
       <c r="AT271" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48734,7 +48722,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -48786,98 +48774,18 @@
       <c r="P272" t="n">
         <v>0</v>
       </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>Japanese Encephalitis</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R272" t="n">
+        <v>0</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ272" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN272" t="b">
-        <v>1</v>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
@@ -48971,17 +48879,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -49006,7 +48914,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -49020,76 +48928,168 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="R273" t="n">
-        <v>0</v>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P273" t="n">
+        <v>0</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
       </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR273" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
       <c r="AT273" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -49121,12 +49121,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -49165,9 +49165,6 @@
       <c r="O274" t="n">
         <v>0</v>
       </c>
-      <c r="P274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0</v>
       </c>
@@ -49176,77 +49173,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA274" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO274" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ274" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS274" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr"/>
       <c r="AT274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49273,7 +49261,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -49325,98 +49313,18 @@
       <c r="P275" t="n">
         <v>0</v>
       </c>
-      <c r="U275" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="V275" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="W275" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X275" t="inlineStr">
-        <is>
-          <t>Japanese Encephalitis</t>
-        </is>
-      </c>
-      <c r="Y275" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z275" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R275" t="n">
+        <v>0</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB275" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD275" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE275" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF275" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG275" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI275" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ275" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK275" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM275" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN275" t="b">
-        <v>1</v>
       </c>
       <c r="AO275" t="inlineStr">
         <is>
@@ -49510,17 +49418,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -49545,7 +49453,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -49559,76 +49467,168 @@
       <c r="O276" t="n">
         <v>0</v>
       </c>
-      <c r="R276" t="n">
-        <v>0</v>
-      </c>
-      <c r="S276" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P276" t="n">
+        <v>0</v>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM276" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN276" t="b">
+        <v>1</v>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR276" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS276" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
       <c r="AT276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -49660,12 +49660,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -49704,9 +49704,6 @@
       <c r="O277" t="n">
         <v>0</v>
       </c>
-      <c r="P277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
@@ -49715,77 +49712,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA277" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ277" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS277" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR277" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr"/>
       <c r="AT277" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49812,7 +49800,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -49864,98 +49852,18 @@
       <c r="P278" t="n">
         <v>0</v>
       </c>
-      <c r="U278" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="V278" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="W278" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X278" t="inlineStr">
-        <is>
-          <t>Japanese Encephalitis</t>
-        </is>
-      </c>
-      <c r="Y278" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z278" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB278" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC278" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD278" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE278" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF278" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG278" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH278" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI278" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ278" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK278" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM278" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN278" t="b">
-        <v>1</v>
       </c>
       <c r="AO278" t="inlineStr">
         <is>
@@ -50049,17 +49957,17 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -50084,7 +49992,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -50098,76 +50006,168 @@
       <c r="O279" t="n">
         <v>0</v>
       </c>
-      <c r="R279" t="n">
-        <v>0</v>
-      </c>
-      <c r="S279" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P279" t="n">
+        <v>0</v>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM279" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN279" t="b">
+        <v>1</v>
       </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR279" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS279" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
       <c r="AT279" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -50199,12 +50199,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -50243,9 +50243,6 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
-      <c r="P280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>0</v>
       </c>
@@ -50254,77 +50251,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA280" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO280" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ280" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS280" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR280" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr"/>
       <c r="AT280" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -50351,7 +50339,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -50403,98 +50391,18 @@
       <c r="P281" t="n">
         <v>0</v>
       </c>
-      <c r="U281" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="V281" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="W281" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X281" t="inlineStr">
-        <is>
-          <t>Japanese Encephalitis</t>
-        </is>
-      </c>
-      <c r="Y281" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z281" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R281" t="n">
+        <v>0</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC281" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD281" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE281" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF281" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG281" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH281" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI281" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ281" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK281" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM281" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN281" t="b">
-        <v>1</v>
       </c>
       <c r="AO281" t="inlineStr">
         <is>
@@ -50588,17 +50496,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -50623,12 +50531,12 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N282" t="n">
@@ -50637,76 +50545,168 @@
       <c r="O282" t="n">
         <v>0</v>
       </c>
-      <c r="R282" t="n">
-        <v>0</v>
-      </c>
-      <c r="S282" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P282" t="n">
+        <v>0</v>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ282" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK282" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM282" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN282" t="b">
+        <v>1</v>
       </c>
       <c r="AO282" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP282" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR282" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS282" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
       <c r="AT282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV282" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA282" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB282" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC282" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -50738,12 +50738,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -50816,42 +50816,42 @@
       </c>
       <c r="AV283" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA283" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB283" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC283" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -50883,12 +50883,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -50913,7 +50913,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -50961,42 +50961,42 @@
       </c>
       <c r="AV284" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA284" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB284" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC284" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -51028,12 +51028,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -51072,9 +51072,6 @@
       <c r="O285" t="n">
         <v>0</v>
       </c>
-      <c r="P285" t="n">
-        <v>0</v>
-      </c>
       <c r="R285" t="n">
         <v>0</v>
       </c>
@@ -51083,77 +51080,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA285" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO285" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ285" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS285" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr"/>
       <c r="AT285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV285" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA285" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB285" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC285" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -51180,7 +51168,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -51232,98 +51220,18 @@
       <c r="P286" t="n">
         <v>0</v>
       </c>
-      <c r="U286" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="V286" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
-        </is>
-      </c>
-      <c r="W286" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X286" t="inlineStr">
-        <is>
-          <t>Japanese Encephalitis</t>
-        </is>
-      </c>
-      <c r="Y286" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z286" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R286" t="n">
+        <v>0</v>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB286" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC286" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD286" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE286" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF286" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG286" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH286" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI286" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ286" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK286" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM286" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN286" t="b">
-        <v>1</v>
       </c>
       <c r="AO286" t="inlineStr">
         <is>
@@ -51389,6 +51297,782 @@
         </is>
       </c>
       <c r="BC286" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>0</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
+      <c r="P287" t="n">
+        <v>0</v>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC287" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD287" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE287" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF287" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG287" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH287" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI287" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ287" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK287" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM287" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN287" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="AT287" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV287" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA287" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB287" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC287" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="R288" t="n">
+        <v>0</v>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR288" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr"/>
+      <c r="AT288" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU288" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV288" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA288" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB288" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC288" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>0</v>
+      </c>
+      <c r="O289" t="n">
+        <v>0</v>
+      </c>
+      <c r="P289" t="n">
+        <v>0</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP289" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ289" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="AT289" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV289" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA289" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB289" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC289" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB290" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC290" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD290" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE290" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF290" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG290" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH290" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI290" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ290" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK290" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM290" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN290" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ290" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="AT290" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU290" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV290" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA290" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB290" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC290" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -51427,7 +52111,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -51510,7 +52194,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10">
@@ -51520,7 +52204,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="11">
@@ -51540,7 +52224,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d020/2026-2029.xlsx
+++ b/diseases/d020/2026-2029.xlsx
@@ -55158,6 +55158,690 @@
         </is>
       </c>
     </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N307" t="n">
+        <v>0</v>
+      </c>
+      <c r="O307" t="n">
+        <v>0</v>
+      </c>
+      <c r="R307" t="n">
+        <v>0</v>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO307" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP307" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR307" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS307" t="inlineStr"/>
+      <c r="AT307" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU307" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV307" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW307" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX307" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY307" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA307" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB307" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC307" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N308" t="n">
+        <v>0</v>
+      </c>
+      <c r="O308" t="n">
+        <v>0</v>
+      </c>
+      <c r="P308" t="n">
+        <v>0</v>
+      </c>
+      <c r="R308" t="n">
+        <v>0</v>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO308" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP308" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ308" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS308" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="AT308" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU308" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV308" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW308" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX308" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY308" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA308" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB308" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC308" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N309" t="n">
+        <v>0</v>
+      </c>
+      <c r="O309" t="n">
+        <v>0</v>
+      </c>
+      <c r="P309" t="n">
+        <v>0</v>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF309" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG309" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH309" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI309" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ309" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK309" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM309" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN309" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO309" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP309" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ309" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS309" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="AT309" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU309" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV309" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW309" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX309" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY309" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA309" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB309" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC309" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N310" t="n">
+        <v>0</v>
+      </c>
+      <c r="O310" t="n">
+        <v>0</v>
+      </c>
+      <c r="R310" t="n">
+        <v>0</v>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO310" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP310" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR310" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS310" t="inlineStr"/>
+      <c r="AT310" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU310" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV310" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW310" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX310" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY310" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA310" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB310" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC310" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -55191,7 +55875,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -55274,7 +55958,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -55284,7 +55968,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11">
@@ -55304,7 +55988,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d020/2026-2029.xlsx
+++ b/diseases/d020/2026-2029.xlsx
@@ -61149,13 +61149,13 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R349" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S349" t="inlineStr">
         <is>
@@ -63312,7 +63312,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d020/2026-2029.xlsx
+++ b/diseases/d020/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1211,6 +1226,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1356,6 +1376,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1501,6 +1526,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1646,6 +1676,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1782,6 +1817,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1927,6 +1967,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2075,6 +2120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5685,6 +5735,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5830,6 +5885,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8146,6 +8206,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8291,6 +8356,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8436,6 +8506,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8581,6 +8656,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8726,6 +8806,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8871,6 +8956,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9016,6 +9106,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9161,6 +9256,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9306,6 +9406,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9454,6 +9559,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13064,6 +13174,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13209,6 +13324,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15525,6 +15645,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15670,6 +15795,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15815,6 +15945,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15960,6 +16095,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16105,6 +16245,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16250,6 +16395,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16395,6 +16545,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16540,6 +16695,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16685,6 +16845,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16833,6 +16998,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20058,6 +20228,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20203,6 +20378,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22910,6 +23090,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23055,6 +23240,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23200,6 +23390,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23345,6 +23540,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23481,6 +23681,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23626,6 +23831,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23771,6 +23981,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23916,6 +24131,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24061,6 +24281,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24209,6 +24434,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27434,6 +27664,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27579,6 +27814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29892,6 +30132,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30037,6 +30282,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30182,6 +30432,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30327,6 +30582,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30472,6 +30732,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30617,6 +30882,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30762,6 +31032,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30907,6 +31182,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31052,6 +31332,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31200,6 +31485,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34810,6 +35100,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34955,6 +35250,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37955,6 +38255,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38100,6 +38405,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38245,6 +38555,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38390,6 +38705,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38535,6 +38855,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38680,6 +39005,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38825,6 +39155,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38970,6 +39305,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39115,6 +39455,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39263,6 +39608,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42488,6 +42838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42633,6 +42988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45079,6 +45439,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45224,6 +45589,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45369,6 +45739,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45514,6 +45889,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45659,6 +46039,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45804,6 +46189,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45949,6 +46339,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46094,6 +46489,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46239,6 +46639,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46387,6 +46792,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49997,6 +50407,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50142,6 +50557,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52733,6 +53153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO299" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52878,6 +53303,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO300" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53023,6 +53453,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53168,6 +53603,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53313,6 +53753,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53449,6 +53894,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53594,6 +54044,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53739,6 +54194,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53884,6 +54344,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54032,6 +54497,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56872,6 +57342,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO323" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -57017,6 +57492,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -59857,6 +60337,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60002,6 +60487,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO341" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60147,6 +60637,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO342" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60292,6 +60787,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO343" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60437,6 +60937,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO344" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60582,6 +61087,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60727,6 +61237,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO346" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -60872,6 +61387,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO347" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61017,6 +61537,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA348" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO348" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -61149,17 +61674,22 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O349" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R349" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S349" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA349" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO349" t="inlineStr">
@@ -63017,118 +63547,517 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N360" t="n">
+        <v>0</v>
+      </c>
+      <c r="O360" t="n">
+        <v>0</v>
+      </c>
+      <c r="P360" t="n">
+        <v>0</v>
+      </c>
+      <c r="R360" t="n">
+        <v>0</v>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO360" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP360" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ360" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS360" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="AT360" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU360" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV360" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW360" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX360" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY360" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA360" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB360" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC360" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N361" t="n">
+        <v>0</v>
+      </c>
+      <c r="O361" t="n">
+        <v>0</v>
+      </c>
+      <c r="P361" t="n">
+        <v>0</v>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB361" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC361" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD361" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE361" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF361" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI361" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ361" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK361" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM361" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN361" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO361" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP361" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ361" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS361" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="AT361" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU361" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV361" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW361" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX361" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY361" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA361" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB361" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC361" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr">
+      <c r="G362" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>D020</t>
-        </is>
-      </c>
-      <c r="I360" t="inlineStr">
-        <is>
-          <t>Japanese Encephalitis</t>
-        </is>
-      </c>
-      <c r="J360" t="inlineStr">
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
         <is>
           <t>流行性乙型脑炎</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr">
+      <c r="K362" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L360" t="inlineStr">
+      <c r="L362" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M360" t="inlineStr">
+      <c r="M362" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N360" t="n">
-        <v>0</v>
-      </c>
-      <c r="O360" t="n">
-        <v>0</v>
-      </c>
-      <c r="R360" t="n">
-        <v>0</v>
-      </c>
-      <c r="S360" t="inlineStr">
+      <c r="N362" t="n">
+        <v>0</v>
+      </c>
+      <c r="O362" t="n">
+        <v>0</v>
+      </c>
+      <c r="R362" t="n">
+        <v>0</v>
+      </c>
+      <c r="S362" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO360" t="inlineStr">
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO362" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP360" t="inlineStr">
+      <c r="AP362" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR360" t="inlineStr">
+      <c r="AR362" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS360" t="inlineStr"/>
-      <c r="AT360" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU360" t="inlineStr">
+      <c r="AS362" t="inlineStr"/>
+      <c r="AT362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU362" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV360" t="inlineStr">
+      <c r="AV362" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW360" t="inlineStr">
+      <c r="AW362" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX360" t="inlineStr">
+      <c r="AX362" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY360" t="inlineStr">
+      <c r="AY362" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ360" t="inlineStr">
+      <c r="AZ362" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA360" t="inlineStr">
+      <c r="BA362" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB360" t="inlineStr">
+      <c r="BB362" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC360" t="inlineStr">
+      <c r="BC362" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -63250,7 +64179,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -63260,7 +64189,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11">
@@ -63280,7 +64209,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
@@ -63312,7 +64241,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d020/2026-2029.xlsx
+++ b/diseases/d020/2026-2029.xlsx
@@ -61674,13 +61674,13 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O349" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R349" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S349" t="inlineStr">
         <is>
@@ -64241,7 +64241,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d020/2026-2029.xlsx
+++ b/diseases/d020/2026-2029.xlsx
@@ -64063,6 +64063,151 @@
         </is>
       </c>
     </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N363" t="n">
+        <v>1</v>
+      </c>
+      <c r="O363" t="n">
+        <v>1</v>
+      </c>
+      <c r="R363" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S363" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO363" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP363" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR363" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS363" t="inlineStr"/>
+      <c r="AT363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU363" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV363" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW363" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX363" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY363" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA363" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB363" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC363" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -64096,7 +64241,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -64179,7 +64324,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -64189,7 +64334,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11">
@@ -64241,7 +64386,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d020/2026-2029.xlsx
+++ b/diseases/d020/2026-2029.xlsx
@@ -61674,13 +61674,13 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O349" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R349" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S349" t="inlineStr">
         <is>
@@ -64205,6 +64205,400 @@
       <c r="BC363" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N364" t="n">
+        <v>0</v>
+      </c>
+      <c r="O364" t="n">
+        <v>0</v>
+      </c>
+      <c r="P364" t="n">
+        <v>0</v>
+      </c>
+      <c r="R364" t="n">
+        <v>0</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO364" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP364" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ364" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="AT364" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU364" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV364" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW364" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX364" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY364" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA364" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB364" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC364" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>japanese-encephalitis</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>D020</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>流行性乙型脑炎</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N365" t="n">
+        <v>0</v>
+      </c>
+      <c r="O365" t="n">
+        <v>0</v>
+      </c>
+      <c r="P365" t="n">
+        <v>0</v>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>Japanese Encephalitis</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB365" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC365" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD365" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE365" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF365" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI365" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ365" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK365" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM365" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN365" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO365" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP365" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ365" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS365" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_JAPANESE_ENCEPHALITIS; SER_SG_HIST_JAPANESE_ENCEPHALITIS</t>
+        </is>
+      </c>
+      <c r="AT365" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU365" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV365" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW365" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX365" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY365" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA365" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB365" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC365" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -64324,7 +64718,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -64334,7 +64728,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11">
@@ -64354,7 +64748,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13">
@@ -64386,7 +64780,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16">
